--- a/input/mapping/039. OCB_GOLD_TCKH_BRANCH_LIST_HOP.xlsx
+++ b/input/mapping/039. OCB_GOLD_TCKH_BRANCH_LIST_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1656" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03F515CE-3582-4FFE-9602-8A72C6194393}"/>
+  <xr:revisionPtr revIDLastSave="1662" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6FC8383-82E9-45B7-BB75-CF919C95EBD2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -254,37 +254,17 @@
       dim.OU_ID           AS OU_ID
     , dim.OU_CODE         AS BRANCH_CODE
     , dim.OU_NM           AS BRANCH_NAME
-    , NVL(dim.PRN_OU_CODE, dim.OU_CODE)     AS PRN_BRANCH_CODE
+    , nvl(dim.PRN_OU_CODE, dim.OU_CODE)     AS PRN_BRANCH_CODE
     , nvl(dim.PRN_OU_NM, dim.OU_NM)       AS PRN_BRANCH_NAME
 FROM CB_OU_DIM dim
-WHERE dim.EFF_TO_DT IS NULL   -- SCD2: chỉ lấy bản ghi còn hiệu lực (NULL = chưa đóng)
-;</t>
+WHERE dim.EFF_TO_DT IS NULL   -- SCD2: chỉ lấy bản ghi còn hiệu lực (NULL = chưa đóng)</t>
   </si>
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,     -- MAX(OU_DIM_ID) + ROW_NUMBER()
-    OU_ID           STRING,     -- branch_hashkey (SHA256)
-    OU_NM           STRING,
-    OU_CODE         STRING,
-    PRN_OU_ID       STRING,
-    PRN_OU_NM       STRING,
-    PRN_OU_CODE     STRING,
-    CB_AREA_ID      INTEGER,
-    CB_AREA_NM      STRING,
-    CRT_TM          TIMESTAMP,
-    EFF_FM_DT       DATE,
-    EFF_TO_DT       DATE,
-    START_WK_DT     DATE,
-    OU_ADR          STRING,
-    OU_PH           STRING
-)
-USING DELTA;
 MERGE INTO CB_OU_DIM tgt
 USING (
     WITH
-    -- STS Hub: khóa có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT branch_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
@@ -292,15 +272,12 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực = Hub LEFT JOIN loại các khóa deleted
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
-        LEFT JOIN sts_deleted d
-            ON h.branch_hashkey = d.branch_hashkey
+        LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite (single-active): làm giàu thuộc tính, bản mới nhất đến :etl_date
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -309,7 +286,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping (single-active)
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -320,18 +296,23 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
+    area_map AS (
+        SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+        FROM ou_area_mapping
+        WHERE CB_AREA_ID IS NOT NULL
+    ),
     source_data AS (
         SELECT
-            h.branch_hashkey                                    AS OU_ID,
-            h.business_key                                      AS OU_CODE,
-            SUBSTRING_INDEX(si.t_company_name, '::', 1)         AS OU_NM,
-            prn_hub.branch_hashkey                              AS PRN_OU_ID,
-            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)     AS PRN_OU_NM,
-            bm.parent_branch_code                               AS PRN_OU_CODE,
+            h.branch_hashkey                                AS OU_ID,
+            h.business_key                                  AS OU_CODE,
+            SUBSTRING_INDEX(si.t_company_name, '::', 1)     AS OU_NM,
+            prn_hub.branch_hashkey                          AS PRN_OU_ID,
+            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1) AS PRN_OU_NM,
+            bm.parent_branch_code                           AS PRN_OU_CODE,
             am.CB_AREA_ID,
             am.CB_AREA_NM,
-            bm.address                                          AS OU_ADR,
-            bm.phone_number                                     AS OU_PH,
+            bm.address                                      AS OU_ADR,
+            bm.phone_number                                 AS OU_PH,
             h.source_event_date
         FROM hub_active h
         LEFT JOIN sat_latest si
@@ -342,15 +323,10 @@
             ON prn_hub.business_key = bm.parent_branch_code
         LEFT JOIN sat_latest prn_si
             ON prn_hub.branch_hashkey = prn_si.branch_hashkey
-        LEFT JOIN ou_area_mapping am
+        LEFT JOIN area_map am
             ON am.OU_ID = h.business_key
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
-    ),
-    -- Max OU_DIM_ID hiện tại
-    max_id AS (
-        SELECT COALESCE(MAX(OU_DIM_ID), 0) AS max_val
-        FROM CB_OU_DIM
     ),
     changed AS (
         SELECT src.OU_ID
@@ -380,9 +356,8 @@
             src.source_event_date,
             src.OU_ADR,
             src.OU_PH,
-            m.max_val + ROW_NUMBER() OVER (ORDER BY src.OU_ID)  AS NEW_OU_DIM_ID
+            uuid()                                              AS NEW_OU_DIM_ID
         FROM source_data src
-        CROSS JOIN max_id m
         LEFT JOIN CB_OU_DIM tgt_chk
             ON  src.OU_ID        = tgt_chk.OU_ID
             AND tgt_chk.EFF_TO_DT IS NULL
@@ -391,8 +366,8 @@
     ),
     close_records AS (
         SELECT
-            'CLOSE'                                             AS rec_type,
-            'D'                                                 AS CDC_FLAG,
+            'CLOSE'                AS rec_type,
+            'D'                    AS CDC_FLAG,
             tgt.OU_ID,
             tgt.OU_NM,
             tgt.OU_CODE,
@@ -401,10 +376,10 @@
             tgt.PRN_OU_CODE,
             tgt.CB_AREA_ID,
             tgt.CB_AREA_NM,
-            tgt.START_WK_DT                                     AS source_event_date,
+            tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            tgt.OU_DIM_ID                                       AS NEW_OU_DIM_ID
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID 
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -413,9 +388,25 @@
                 OR src.OU_ID IS NULL
               )
     )
-    SELECT * FROM new_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM new_records
     UNION ALL
-    SELECT * FROM close_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM close_records
 ) src
 ON  tgt.OU_ID     = src.OU_ID
 AND tgt.EFF_TO_DT IS NULL
@@ -449,8 +440,7 @@
 WHEN MATCHED AND src.rec_type = 'CLOSE' THEN
     UPDATE SET
         tgt.EFF_TO_DT = DATE_SUB(TO_DATE(:etl_date, 'yyyyMMdd'), 1),
-        tgt.CRT_TM    = CURRENT_TIMESTAMP()
-;</t>
+        tgt.CRT_TM    = CURRENT_TIMESTAMP()</t>
   </si>
   <si>
     <t>JOIN SCHEMA</t>
@@ -2992,7 +2982,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="269">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3422,265 +3412,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3725,9 +3456,269 @@
     <xf numFmtId="49" fontId="27" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3746,7 +3737,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4113,16 +4104,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="173" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
       <c r="I1" s="154"/>
       <c r="J1" s="38"/>
       <c r="K1" s="38"/>
@@ -4165,87 +4156,87 @@
       <c r="AV1" s="38"/>
     </row>
     <row r="2" spans="1:48" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="190" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="179"/>
-      <c r="C2" s="163" t="s">
+      <c r="B2" s="191"/>
+      <c r="C2" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="178" t="s">
+      <c r="D2" s="190" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="184"/>
-      <c r="F2" s="163" t="s">
+      <c r="E2" s="196"/>
+      <c r="F2" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="166" t="s">
+      <c r="G2" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="167"/>
+      <c r="H2" s="179"/>
     </row>
     <row r="3" spans="1:48">
-      <c r="A3" s="180"/>
-      <c r="B3" s="181"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="180"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="168"/>
-      <c r="H3" s="169"/>
+      <c r="A3" s="192"/>
+      <c r="B3" s="193"/>
+      <c r="C3" s="176"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="197"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="180"/>
+      <c r="H3" s="181"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="180"/>
-      <c r="B4" s="181"/>
-      <c r="C4" s="164"/>
-      <c r="D4" s="180"/>
-      <c r="E4" s="185"/>
+      <c r="A4" s="192"/>
+      <c r="B4" s="193"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="197"/>
       <c r="F4" s="153"/>
-      <c r="G4" s="170"/>
-      <c r="H4" s="171"/>
+      <c r="G4" s="182"/>
+      <c r="H4" s="183"/>
     </row>
     <row r="5" spans="1:48">
-      <c r="A5" s="180"/>
-      <c r="B5" s="181"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="185"/>
+      <c r="A5" s="192"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="176"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="197"/>
       <c r="G5" s="123"/>
       <c r="H5" s="123"/>
     </row>
     <row r="6" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A6" s="180"/>
-      <c r="B6" s="181"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="180"/>
-      <c r="E6" s="185"/>
-      <c r="F6" s="163" t="s">
+      <c r="A6" s="192"/>
+      <c r="B6" s="193"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="192"/>
+      <c r="E6" s="197"/>
+      <c r="F6" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="172" t="s">
+      <c r="G6" s="184" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="173"/>
+      <c r="H6" s="185"/>
     </row>
     <row r="7" spans="1:48">
-      <c r="A7" s="180"/>
-      <c r="B7" s="181"/>
-      <c r="C7" s="164"/>
-      <c r="D7" s="180"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="174"/>
-      <c r="H7" s="175"/>
+      <c r="A7" s="192"/>
+      <c r="B7" s="193"/>
+      <c r="C7" s="176"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="176"/>
+      <c r="G7" s="186"/>
+      <c r="H7" s="187"/>
     </row>
     <row r="8" spans="1:48">
-      <c r="A8" s="182"/>
-      <c r="B8" s="183"/>
-      <c r="C8" s="165"/>
-      <c r="D8" s="182"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="176"/>
-      <c r="H8" s="177"/>
+      <c r="A8" s="194"/>
+      <c r="B8" s="195"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="194"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="177"/>
+      <c r="G8" s="188"/>
+      <c r="H8" s="189"/>
     </row>
     <row r="12" spans="1:48">
       <c r="A12" s="124"/>
@@ -4301,18 +4292,18 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="243" t="s">
+      <c r="A19" s="261" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="243" t="s">
+      <c r="B19" s="261" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="243" t="s">
+      <c r="A20" s="261" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="243" t="s">
+      <c r="B20" s="261" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4407,8 +4398,8 @@
       </c>
       <c r="B6" s="57"/>
       <c r="C6" s="57"/>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
+      <c r="D6" s="239"/>
+      <c r="E6" s="239"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1">
@@ -4421,10 +4412,10 @@
       <c r="C7" s="58" t="s">
         <v>179</v>
       </c>
-      <c r="D7" s="224" t="s">
+      <c r="D7" s="240" t="s">
         <v>180</v>
       </c>
-      <c r="E7" s="225"/>
+      <c r="E7" s="241"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
@@ -4437,10 +4428,10 @@
       <c r="C8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="221" t="s">
+      <c r="D8" s="237" t="s">
         <v>368</v>
       </c>
-      <c r="E8" s="222"/>
+      <c r="E8" s="238"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1">
@@ -4453,10 +4444,10 @@
       <c r="C9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="221" t="s">
+      <c r="D9" s="237" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="222"/>
+      <c r="E9" s="238"/>
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1">
@@ -4469,10 +4460,10 @@
       <c r="C10" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="221" t="s">
+      <c r="D10" s="237" t="s">
         <v>102</v>
       </c>
-      <c r="E10" s="222"/>
+      <c r="E10" s="238"/>
     </row>
     <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="A11" s="8" t="s">
@@ -4484,10 +4475,10 @@
       <c r="C11" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="221" t="s">
+      <c r="D11" s="237" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="222"/>
+      <c r="E11" s="238"/>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="A12" s="8" t="s">
@@ -4499,10 +4490,10 @@
       <c r="C12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="221" t="s">
+      <c r="D12" s="237" t="s">
         <v>370</v>
       </c>
-      <c r="E12" s="222"/>
+      <c r="E12" s="238"/>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="A13" s="8" t="s">
@@ -4514,10 +4505,10 @@
       <c r="C13" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="221" t="s">
+      <c r="D13" s="237" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="222"/>
+      <c r="E13" s="238"/>
     </row>
     <row r="14" spans="1:7" ht="70.5" customHeight="1">
       <c r="A14" s="8" t="s">
@@ -4529,10 +4520,10 @@
       <c r="C14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="221" t="s">
+      <c r="D14" s="237" t="s">
         <v>372</v>
       </c>
-      <c r="E14" s="222"/>
+      <c r="E14" s="238"/>
     </row>
     <row r="15" spans="1:7" ht="14.45" customHeight="1"/>
   </sheetData>
@@ -4782,13 +4773,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="226" t="s">
+      <c r="A1" s="242" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
+      <c r="B1" s="243"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="243"/>
+      <c r="E1" s="243"/>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="60" t="s">
@@ -4830,13 +4821,13 @@
       <c r="E4" s="62"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="227" t="s">
+      <c r="A5" s="243" t="s">
         <v>381</v>
       </c>
-      <c r="B5" s="227"/>
-      <c r="C5" s="227"/>
-      <c r="D5" s="227"/>
-      <c r="E5" s="227"/>
+      <c r="B5" s="243"/>
+      <c r="C5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="60" t="s">
@@ -4969,14 +4960,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="228" t="s">
+      <c r="A1" s="244" t="s">
         <v>388</v>
       </c>
-      <c r="B1" s="229"/>
-      <c r="C1" s="229"/>
-      <c r="D1" s="229"/>
-      <c r="E1" s="229"/>
-      <c r="F1" s="229"/>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="65" t="s">
@@ -4985,10 +4976,10 @@
       <c r="B2" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="246" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="231"/>
+      <c r="D2" s="247"/>
       <c r="E2" s="65" t="s">
         <v>31</v>
       </c>
@@ -5003,8 +4994,8 @@
       <c r="B3" s="67" t="s">
         <v>389</v>
       </c>
-      <c r="C3" s="232"/>
-      <c r="D3" s="233"/>
+      <c r="C3" s="248"/>
+      <c r="D3" s="249"/>
       <c r="E3" s="67" t="s">
         <v>35</v>
       </c>
@@ -5021,13 +5012,13 @@
       <c r="F4" s="68"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="229" t="s">
+      <c r="A5" s="245" t="s">
         <v>391</v>
       </c>
-      <c r="B5" s="229"/>
-      <c r="C5" s="229"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
       <c r="F5" s="69"/>
     </row>
     <row r="6" spans="1:6">
@@ -6287,14 +6278,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="250" t="s">
         <v>456</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
+      <c r="B1" s="251"/>
+      <c r="C1" s="251"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="251"/>
+      <c r="F1" s="251"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="59" t="s">
@@ -6303,10 +6294,10 @@
       <c r="B2" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="235"/>
+      <c r="D2" s="251"/>
       <c r="E2" s="59" t="s">
         <v>31</v>
       </c>
@@ -6323,13 +6314,13 @@
       <c r="F3" s="74"/>
     </row>
     <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="235" t="s">
+      <c r="A4" s="251" t="s">
         <v>457</v>
       </c>
-      <c r="B4" s="235"/>
-      <c r="C4" s="235"/>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
+      <c r="B4" s="251"/>
+      <c r="C4" s="251"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
       <c r="F4" s="75"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
@@ -7580,13 +7571,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A1" s="236" t="s">
+      <c r="A1" s="252" t="s">
         <v>459</v>
       </c>
-      <c r="B1" s="237"/>
-      <c r="C1" s="237"/>
-      <c r="D1" s="237"/>
-      <c r="E1" s="237"/>
+      <c r="B1" s="253"/>
+      <c r="C1" s="253"/>
+      <c r="D1" s="253"/>
+      <c r="E1" s="253"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="80" t="s">
@@ -7621,13 +7612,13 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="238" t="s">
+      <c r="A4" s="254" t="s">
         <v>462</v>
       </c>
-      <c r="B4" s="239"/>
-      <c r="C4" s="239"/>
-      <c r="D4" s="239"/>
-      <c r="E4" s="240"/>
+      <c r="B4" s="255"/>
+      <c r="C4" s="255"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="256"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="80" t="s">
@@ -7743,13 +7734,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="47.25" customHeight="1">
-      <c r="A1" s="241" t="s">
+      <c r="A1" s="257" t="s">
         <v>466</v>
       </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="258"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="84" t="s">
@@ -7776,13 +7767,13 @@
       <c r="E3" s="85"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="235" t="s">
+      <c r="A5" s="251" t="s">
         <v>467</v>
       </c>
-      <c r="B5" s="235"/>
-      <c r="C5" s="235"/>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
+      <c r="B5" s="251"/>
+      <c r="C5" s="251"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="59" t="s">
@@ -8078,7 +8069,7 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="244" t="s">
+      <c r="C3" s="157" t="s">
         <v>22</v>
       </c>
       <c r="D3" t="s">
@@ -8092,7 +8083,7 @@
       <c r="B4" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="259" t="s">
         <v>25</v>
       </c>
     </row>
@@ -8128,16 +8119,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="199" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="188"/>
-      <c r="G1" s="189"/>
-      <c r="H1" s="261"/>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="201"/>
+      <c r="H1" s="262"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="92" t="s">
@@ -8152,12 +8143,12 @@
       <c r="D2" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="188" t="s">
+      <c r="E2" s="200" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="188"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="261"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="202"/>
+      <c r="H2" s="262"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="89">
@@ -8172,10 +8163,10 @@
       <c r="D3" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="191"/>
-      <c r="F3" s="191"/>
-      <c r="G3" s="192"/>
-      <c r="H3" s="261"/>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="262"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
       <c r="A4" s="89">
@@ -8190,24 +8181,24 @@
       <c r="D4" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="191" t="s">
+      <c r="E4" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="191"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="261"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="262"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A5" s="193" t="s">
+      <c r="A5" s="205" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="194"/>
-      <c r="C5" s="194"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="195"/>
-      <c r="H5" s="261"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="206"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="262"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="92" t="s">
@@ -8231,7 +8222,7 @@
       <c r="G6" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="261"/>
+      <c r="H6" s="262"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="89">
@@ -8255,7 +8246,7 @@
       <c r="G7" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="261"/>
+      <c r="H7" s="262"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="89">
@@ -8279,7 +8270,7 @@
       <c r="G8" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="261"/>
+      <c r="H8" s="262"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="89">
@@ -8303,7 +8294,7 @@
       <c r="G9" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="261"/>
+      <c r="H9" s="262"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="89">
@@ -8327,7 +8318,7 @@
       <c r="G10" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="261"/>
+      <c r="H10" s="262"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="89">
@@ -8351,7 +8342,7 @@
       <c r="G11" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="261"/>
+      <c r="H11" s="262"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="89">
@@ -8375,7 +8366,7 @@
       <c r="G12" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="261"/>
+      <c r="H12" s="262"/>
     </row>
     <row r="13" spans="1:8" ht="60.75">
       <c r="A13" s="89">
@@ -8399,7 +8390,7 @@
       <c r="G13" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="261"/>
+      <c r="H13" s="262"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="89">
@@ -8423,7 +8414,7 @@
       <c r="G14" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="261"/>
+      <c r="H14" s="262"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="89">
@@ -8447,7 +8438,7 @@
       <c r="G15" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="261"/>
+      <c r="H15" s="262"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="89">
@@ -8471,7 +8462,7 @@
       <c r="G16" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="261"/>
+      <c r="H16" s="262"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="89">
@@ -8495,7 +8486,7 @@
       <c r="G17" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="261"/>
+      <c r="H17" s="262"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="89">
@@ -8519,7 +8510,7 @@
       <c r="G18" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="261"/>
+      <c r="H18" s="262"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="89">
@@ -8543,7 +8534,7 @@
       <c r="G19" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H19" s="261"/>
+      <c r="H19" s="262"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="89">
@@ -8567,7 +8558,7 @@
       <c r="G20" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H20" s="261"/>
+      <c r="H20" s="262"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="89">
@@ -8591,7 +8582,7 @@
       <c r="G21" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="261"/>
+      <c r="H21" s="262"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="89">
@@ -8615,7 +8606,7 @@
       <c r="G22" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="261"/>
+      <c r="H22" s="262"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="89">
@@ -8639,7 +8630,7 @@
       <c r="G23" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H23" s="261"/>
+      <c r="H23" s="262"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="89">
@@ -8663,7 +8654,7 @@
       <c r="G24" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H24" s="261"/>
+      <c r="H24" s="262"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="89">
@@ -8687,7 +8678,7 @@
       <c r="G25" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H25" s="261"/>
+      <c r="H25" s="262"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="89">
@@ -8711,7 +8702,7 @@
       <c r="G26" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H26" s="261"/>
+      <c r="H26" s="262"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="89">
@@ -8735,7 +8726,7 @@
       <c r="G27" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H27" s="261"/>
+      <c r="H27" s="262"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="89">
@@ -8759,7 +8750,7 @@
       <c r="G28" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H28" s="261"/>
+      <c r="H28" s="262"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="89">
@@ -8783,7 +8774,7 @@
       <c r="G29" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H29" s="261"/>
+      <c r="H29" s="262"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="89">
@@ -8807,7 +8798,7 @@
       <c r="G30" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H30" s="261"/>
+      <c r="H30" s="262"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="89">
@@ -8831,7 +8822,7 @@
       <c r="G31" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H31" s="261"/>
+      <c r="H31" s="262"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="89">
@@ -8855,7 +8846,7 @@
       <c r="G32" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H32" s="261"/>
+      <c r="H32" s="262"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="89">
@@ -8879,7 +8870,7 @@
       <c r="G33" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H33" s="261"/>
+      <c r="H33" s="262"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="89">
@@ -8903,7 +8894,7 @@
       <c r="G34" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H34" s="261"/>
+      <c r="H34" s="262"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="89">
@@ -8927,7 +8918,7 @@
       <c r="G35" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H35" s="261"/>
+      <c r="H35" s="262"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="89">
@@ -8951,7 +8942,7 @@
       <c r="G36" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H36" s="261"/>
+      <c r="H36" s="262"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="89">
@@ -8975,7 +8966,7 @@
       <c r="G37" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H37" s="261"/>
+      <c r="H37" s="262"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="89">
@@ -8999,7 +8990,7 @@
       <c r="G38" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H38" s="261"/>
+      <c r="H38" s="262"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="89">
@@ -9023,7 +9014,7 @@
       <c r="G39" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H39" s="261"/>
+      <c r="H39" s="262"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="89">
@@ -9047,7 +9038,7 @@
       <c r="G40" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H40" s="261"/>
+      <c r="H40" s="262"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="89">
@@ -9071,7 +9062,7 @@
       <c r="G41" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H41" s="261"/>
+      <c r="H41" s="262"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="89">
@@ -9095,7 +9086,7 @@
       <c r="G42" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H42" s="261"/>
+      <c r="H42" s="262"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="89">
@@ -9119,7 +9110,7 @@
       <c r="G43" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H43" s="261"/>
+      <c r="H43" s="262"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="89">
@@ -9143,7 +9134,7 @@
       <c r="G44" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H44" s="261"/>
+      <c r="H44" s="262"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="89">
@@ -9167,7 +9158,7 @@
       <c r="G45" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H45" s="261"/>
+      <c r="H45" s="262"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="89">
@@ -9191,7 +9182,7 @@
       <c r="G46" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H46" s="261"/>
+      <c r="H46" s="262"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="89">
@@ -9215,7 +9206,7 @@
       <c r="G47" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H47" s="261"/>
+      <c r="H47" s="262"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="89">
@@ -9239,7 +9230,7 @@
       <c r="G48" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H48" s="261"/>
+      <c r="H48" s="262"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="89">
@@ -9263,7 +9254,7 @@
       <c r="G49" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H49" s="261"/>
+      <c r="H49" s="262"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="89">
@@ -9287,7 +9278,7 @@
       <c r="G50" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H50" s="261"/>
+      <c r="H50" s="262"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="89">
@@ -9311,7 +9302,7 @@
       <c r="G51" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H51" s="261"/>
+      <c r="H51" s="262"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="89">
@@ -9335,7 +9326,7 @@
       <c r="G52" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H52" s="261"/>
+      <c r="H52" s="262"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="89">
@@ -9359,7 +9350,7 @@
       <c r="G53" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H53" s="261"/>
+      <c r="H53" s="262"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="89">
@@ -9383,7 +9374,7 @@
       <c r="G54" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H54" s="261"/>
+      <c r="H54" s="262"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="89">
@@ -9407,7 +9398,7 @@
       <c r="G55" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H55" s="261"/>
+      <c r="H55" s="262"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="89">
@@ -9431,7 +9422,7 @@
       <c r="G56" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H56" s="261"/>
+      <c r="H56" s="262"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="89">
@@ -9455,7 +9446,7 @@
       <c r="G57" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="H57" s="261"/>
+      <c r="H57" s="262"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="120">
@@ -9479,137 +9470,137 @@
       <c r="G58" s="121" t="s">
         <v>52</v>
       </c>
-      <c r="H58" s="261"/>
+      <c r="H58" s="262"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="262">
+      <c r="A59" s="263">
         <v>53</v>
       </c>
-      <c r="B59" s="263" t="s">
+      <c r="B59" s="264" t="s">
         <v>47</v>
       </c>
-      <c r="C59" s="264" t="s">
+      <c r="C59" s="265" t="s">
         <v>160</v>
       </c>
-      <c r="D59" s="265" t="s">
+      <c r="D59" s="266" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="266" t="s">
-        <v>50</v>
-      </c>
-      <c r="F59" s="263" t="s">
+      <c r="E59" s="267" t="s">
+        <v>50</v>
+      </c>
+      <c r="F59" s="264" t="s">
         <v>161</v>
       </c>
-      <c r="G59" s="263" t="s">
+      <c r="G59" s="264" t="s">
         <v>52</v>
       </c>
-      <c r="H59" s="261"/>
+      <c r="H59" s="262"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="262">
+      <c r="A60" s="263">
         <v>54</v>
       </c>
-      <c r="B60" s="263" t="s">
+      <c r="B60" s="264" t="s">
         <v>47</v>
       </c>
-      <c r="C60" s="264" t="s">
+      <c r="C60" s="265" t="s">
         <v>162</v>
       </c>
-      <c r="D60" s="265" t="s">
+      <c r="D60" s="266" t="s">
         <v>49</v>
       </c>
-      <c r="E60" s="266" t="s">
-        <v>50</v>
-      </c>
-      <c r="F60" s="263" t="s">
+      <c r="E60" s="267" t="s">
+        <v>50</v>
+      </c>
+      <c r="F60" s="264" t="s">
         <v>163</v>
       </c>
-      <c r="G60" s="263" t="s">
+      <c r="G60" s="264" t="s">
         <v>52</v>
       </c>
-      <c r="H60" s="261"/>
+      <c r="H60" s="262"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="262">
+      <c r="A61" s="263">
         <v>55</v>
       </c>
-      <c r="B61" s="263" t="s">
+      <c r="B61" s="264" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="264" t="s">
+      <c r="C61" s="265" t="s">
         <v>164</v>
       </c>
-      <c r="D61" s="265" t="s">
+      <c r="D61" s="266" t="s">
         <v>49</v>
       </c>
-      <c r="E61" s="266" t="s">
-        <v>50</v>
-      </c>
-      <c r="F61" s="263" t="s">
+      <c r="E61" s="267" t="s">
+        <v>50</v>
+      </c>
+      <c r="F61" s="264" t="s">
         <v>165</v>
       </c>
-      <c r="G61" s="263" t="s">
+      <c r="G61" s="264" t="s">
         <v>52</v>
       </c>
-      <c r="H61" s="261"/>
+      <c r="H61" s="262"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="262">
+      <c r="A62" s="263">
         <v>56</v>
       </c>
-      <c r="B62" s="263" t="s">
+      <c r="B62" s="264" t="s">
         <v>47</v>
       </c>
-      <c r="C62" s="264" t="s">
+      <c r="C62" s="265" t="s">
         <v>166</v>
       </c>
-      <c r="D62" s="265" t="s">
+      <c r="D62" s="266" t="s">
         <v>82</v>
       </c>
-      <c r="E62" s="266" t="s">
-        <v>50</v>
-      </c>
-      <c r="F62" s="263" t="s">
+      <c r="E62" s="267" t="s">
+        <v>50</v>
+      </c>
+      <c r="F62" s="264" t="s">
         <v>167</v>
       </c>
-      <c r="G62" s="263" t="s">
+      <c r="G62" s="264" t="s">
         <v>52</v>
       </c>
-      <c r="H62" s="261"/>
+      <c r="H62" s="262"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="262">
+      <c r="A63" s="263">
         <v>57</v>
       </c>
-      <c r="B63" s="263" t="s">
+      <c r="B63" s="264" t="s">
         <v>47</v>
       </c>
-      <c r="C63" s="264" t="s">
+      <c r="C63" s="265" t="s">
         <v>168</v>
       </c>
-      <c r="D63" s="265" t="s">
+      <c r="D63" s="266" t="s">
         <v>49</v>
       </c>
-      <c r="E63" s="266" t="s">
-        <v>50</v>
-      </c>
-      <c r="F63" s="263" t="s">
+      <c r="E63" s="267" t="s">
+        <v>50</v>
+      </c>
+      <c r="F63" s="264" t="s">
         <v>169</v>
       </c>
-      <c r="G63" s="263" t="s">
+      <c r="G63" s="264" t="s">
         <v>52</v>
       </c>
-      <c r="H63" s="261"/>
+      <c r="H63" s="262"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="267"/>
-      <c r="B64" s="261"/>
-      <c r="C64" s="267"/>
-      <c r="D64" s="267"/>
-      <c r="E64" s="261"/>
-      <c r="F64" s="261"/>
-      <c r="G64" s="261"/>
-      <c r="H64" s="268"/>
+      <c r="A64" s="268"/>
+      <c r="B64" s="262"/>
+      <c r="C64" s="268"/>
+      <c r="D64" s="268"/>
+      <c r="E64" s="262"/>
+      <c r="F64" s="262"/>
+      <c r="G64" s="262"/>
+      <c r="H64" s="269"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9637,14 +9628,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="208" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="197"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
+      <c r="B1" s="209"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="209"/>
+      <c r="E1" s="209"/>
+      <c r="F1" s="209"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
@@ -9654,10 +9645,10 @@
       <c r="B2" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="198" t="s">
+      <c r="C2" s="210" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="199"/>
+      <c r="D2" s="211"/>
       <c r="E2" s="39" t="s">
         <v>31</v>
       </c>
@@ -9673,10 +9664,10 @@
       <c r="B3" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="C3" s="200" t="s">
+      <c r="C3" s="212" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="201"/>
+      <c r="D3" s="213"/>
       <c r="E3" s="40" t="s">
         <v>35</v>
       </c>
@@ -9692,10 +9683,10 @@
       <c r="B4" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="212" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="201"/>
+      <c r="D4" s="213"/>
       <c r="E4" s="40" t="s">
         <v>38</v>
       </c>
@@ -9704,14 +9695,14 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="197" t="s">
+      <c r="A5" s="209" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="197"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="197"/>
-      <c r="F5" s="197"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="39" t="s">
@@ -9841,14 +9832,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="214" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
     </row>
     <row r="2" spans="1:6" ht="24.75" customHeight="1">
       <c r="A2" s="45" t="s">
@@ -9857,10 +9848,10 @@
       <c r="B2" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="204" t="s">
+      <c r="C2" s="216" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="205"/>
+      <c r="D2" s="217"/>
       <c r="E2" s="45" t="s">
         <v>31</v>
       </c>
@@ -9875,10 +9866,10 @@
       <c r="B3" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="206" t="s">
+      <c r="C3" s="218" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="207"/>
+      <c r="D3" s="219"/>
       <c r="E3" s="46" t="s">
         <v>35</v>
       </c>
@@ -9891,10 +9882,10 @@
       <c r="B4" s="49" t="s">
         <v>195</v>
       </c>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="220" t="s">
         <v>196</v>
       </c>
-      <c r="D4" s="209"/>
+      <c r="D4" s="221"/>
       <c r="E4" s="48" t="s">
         <v>197</v>
       </c>
@@ -9903,22 +9894,22 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A5" s="268"/>
-      <c r="B5" s="268"/>
-      <c r="C5" s="268"/>
-      <c r="D5" s="268"/>
-      <c r="E5" s="268"/>
-      <c r="F5" s="268"/>
+      <c r="A5" s="269"/>
+      <c r="B5" s="269"/>
+      <c r="C5" s="269"/>
+      <c r="D5" s="269"/>
+      <c r="E5" s="269"/>
+      <c r="F5" s="269"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="204" t="s">
+      <c r="A7" s="216" t="s">
         <v>199</v>
       </c>
-      <c r="B7" s="210"/>
-      <c r="C7" s="210"/>
-      <c r="D7" s="210"/>
-      <c r="E7" s="210"/>
-      <c r="F7" s="268"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="222"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="269"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="45" t="s">
@@ -9936,7 +9927,7 @@
       <c r="E8" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="F8" s="268"/>
+      <c r="F8" s="269"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="50" t="s">
@@ -9954,7 +9945,7 @@
       <c r="E9" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="F9" s="268"/>
+      <c r="F9" s="269"/>
     </row>
     <row r="10" spans="1:6" ht="60.75">
       <c r="A10" s="50" t="s">
@@ -9972,7 +9963,7 @@
       <c r="E10" s="53" t="s">
         <v>203</v>
       </c>
-      <c r="F10" s="268"/>
+      <c r="F10" s="269"/>
     </row>
     <row r="11" spans="1:6" ht="91.5">
       <c r="A11" s="50" t="s">
@@ -9990,7 +9981,7 @@
       <c r="E11" s="53" t="s">
         <v>206</v>
       </c>
-      <c r="F11" s="268"/>
+      <c r="F11" s="269"/>
     </row>
     <row r="12" spans="1:6" ht="121.5">
       <c r="A12" s="50" t="s">
@@ -10008,7 +9999,7 @@
       <c r="E12" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="F12" s="268"/>
+      <c r="F12" s="269"/>
     </row>
     <row r="13" spans="1:6" ht="76.5">
       <c r="A13" s="50" t="s">
@@ -10026,7 +10017,7 @@
       <c r="E13" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="F13" s="268"/>
+      <c r="F13" s="269"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="50" t="s">
@@ -10044,7 +10035,7 @@
       <c r="E14" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="F14" s="268"/>
+      <c r="F14" s="269"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="50" t="s">
@@ -10062,7 +10053,7 @@
       <c r="E15" s="53" t="s">
         <v>216</v>
       </c>
-      <c r="F15" s="268"/>
+      <c r="F15" s="269"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10089,13 +10080,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="213" t="s">
+      <c r="A1" s="225" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="214"/>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="215"/>
+      <c r="B1" s="226"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="227"/>
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6">
@@ -10196,39 +10187,39 @@
       <c r="E7" s="29"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="213" t="s">
+      <c r="A8" s="225" t="s">
         <v>226</v>
       </c>
-      <c r="B8" s="214"/>
-      <c r="C8" s="214"/>
-      <c r="D8" s="214"/>
-      <c r="E8" s="214"/>
+      <c r="B8" s="226"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="226"/>
+      <c r="E8" s="226"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="216" t="s">
+      <c r="A9" s="228" t="s">
         <v>227</v>
       </c>
-      <c r="B9" s="217" t="s">
+      <c r="B9" s="229" t="s">
         <v>228</v>
       </c>
-      <c r="C9" s="217" t="s">
+      <c r="C9" s="229" t="s">
         <v>179</v>
       </c>
-      <c r="D9" s="218" t="s">
+      <c r="D9" s="230" t="s">
         <v>180</v>
       </c>
-      <c r="E9" s="218" t="s">
+      <c r="E9" s="230" t="s">
         <v>229</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="216"/>
-      <c r="B10" s="217"/>
-      <c r="C10" s="217"/>
-      <c r="D10" s="219"/>
-      <c r="E10" s="219"/>
+      <c r="A10" s="228"/>
+      <c r="B10" s="229"/>
+      <c r="C10" s="229"/>
+      <c r="D10" s="231"/>
+      <c r="E10" s="231"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6">
@@ -11258,13 +11249,13 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="211" t="s">
+      <c r="A68" s="223" t="s">
         <v>246</v>
       </c>
-      <c r="B68" s="212"/>
-      <c r="C68" s="212"/>
-      <c r="D68" s="212"/>
-      <c r="E68" s="212"/>
+      <c r="B68" s="224"/>
+      <c r="C68" s="224"/>
+      <c r="D68" s="224"/>
+      <c r="E68" s="224"/>
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6">
@@ -12313,13 +12304,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="232" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="159"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="234"/>
       <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6">
@@ -12368,13 +12359,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="160" t="s">
+      <c r="A5" s="235" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="160"/>
-      <c r="C5" s="160"/>
-      <c r="D5" s="160"/>
-      <c r="E5" s="160"/>
+      <c r="B5" s="235"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
       <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6">
@@ -12557,13 +12548,13 @@
       <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="220" t="s">
+      <c r="A5" s="236" t="s">
         <v>226</v>
       </c>
-      <c r="B5" s="220"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="220"/>
-      <c r="E5" s="220"/>
+      <c r="B5" s="236"/>
+      <c r="C5" s="236"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
     </row>
     <row r="6" spans="1:5" ht="24.75">
       <c r="A6" s="21" t="s">
@@ -12689,233 +12680,233 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="245" t="s">
+      <c r="A1" s="158" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="245"/>
-      <c r="C1" s="245"/>
-      <c r="D1" s="245"/>
-      <c r="E1" s="245"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
       <c r="F1" s="142"/>
       <c r="G1" s="101"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="246" t="s">
+      <c r="A2" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="245" t="s">
+      <c r="B2" s="158" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="245" t="s">
+      <c r="D2" s="158" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="247" t="s">
+      <c r="E2" s="160" t="s">
         <v>32</v>
       </c>
       <c r="F2" s="102"/>
       <c r="G2" s="101"/>
     </row>
     <row r="3" spans="1:8" ht="152.25">
-      <c r="A3" s="248">
+      <c r="A3" s="161">
         <v>1</v>
       </c>
-      <c r="B3" s="249" t="s">
+      <c r="B3" s="162" t="s">
         <v>298</v>
       </c>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="161" t="s">
         <v>299</v>
       </c>
-      <c r="D3" s="250" t="s">
+      <c r="D3" s="163" t="s">
         <v>300</v>
       </c>
-      <c r="E3" s="251" t="s">
+      <c r="E3" s="164" t="s">
         <v>301</v>
       </c>
       <c r="F3" s="155"/>
       <c r="G3" s="101"/>
     </row>
     <row r="4" spans="1:8" ht="137.25">
-      <c r="A4" s="252">
+      <c r="A4" s="165">
         <v>2</v>
       </c>
-      <c r="B4" s="253" t="s">
+      <c r="B4" s="166" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="254" t="s">
+      <c r="C4" s="167" t="s">
         <v>303</v>
       </c>
-      <c r="D4" s="254" t="s">
+      <c r="D4" s="167" t="s">
         <v>300</v>
       </c>
-      <c r="E4" s="255" t="s">
+      <c r="E4" s="168" t="s">
         <v>304</v>
       </c>
       <c r="G4" s="103"/>
     </row>
     <row r="5" spans="1:8" ht="167.25">
-      <c r="A5" s="252">
+      <c r="A5" s="165">
         <v>3</v>
       </c>
-      <c r="B5" s="253" t="s">
+      <c r="B5" s="166" t="s">
         <v>305</v>
       </c>
-      <c r="C5" s="254" t="s">
+      <c r="C5" s="167" t="s">
         <v>306</v>
       </c>
-      <c r="D5" s="254" t="s">
+      <c r="D5" s="167" t="s">
         <v>300</v>
       </c>
-      <c r="E5" s="255" t="s">
+      <c r="E5" s="168" t="s">
         <v>307</v>
       </c>
       <c r="F5" s="102"/>
       <c r="G5" s="103"/>
     </row>
     <row r="6" spans="1:8" ht="229.5">
-      <c r="A6" s="252">
+      <c r="A6" s="165">
         <v>4</v>
       </c>
-      <c r="B6" s="253" t="s">
+      <c r="B6" s="166" t="s">
         <v>308</v>
       </c>
-      <c r="C6" s="254" t="s">
+      <c r="C6" s="167" t="s">
         <v>309</v>
       </c>
-      <c r="D6" s="254" t="s">
+      <c r="D6" s="167" t="s">
         <v>300</v>
       </c>
-      <c r="E6" s="255" t="s">
+      <c r="E6" s="168" t="s">
         <v>310</v>
       </c>
       <c r="F6" s="102"/>
       <c r="G6" s="103"/>
     </row>
     <row r="7" spans="1:8" ht="409.6">
-      <c r="A7" s="256">
+      <c r="A7" s="169">
         <v>5</v>
       </c>
-      <c r="B7" s="253" t="s">
+      <c r="B7" s="166" t="s">
         <v>311</v>
       </c>
-      <c r="C7" s="257" t="s">
+      <c r="C7" s="170" t="s">
         <v>312</v>
       </c>
-      <c r="D7" s="257" t="s">
+      <c r="D7" s="170" t="s">
         <v>300</v>
       </c>
-      <c r="E7" s="258" t="s">
+      <c r="E7" s="171" t="s">
         <v>313</v>
       </c>
       <c r="F7" s="102"/>
       <c r="G7" s="103"/>
     </row>
     <row r="8" spans="1:8" ht="76.5">
-      <c r="A8" s="256">
+      <c r="A8" s="169">
         <v>6</v>
       </c>
-      <c r="B8" s="253" t="s">
+      <c r="B8" s="166" t="s">
         <v>314</v>
       </c>
-      <c r="C8" s="257" t="s">
+      <c r="C8" s="170" t="s">
         <v>315</v>
       </c>
-      <c r="D8" s="257" t="s">
+      <c r="D8" s="170" t="s">
         <v>300</v>
       </c>
-      <c r="E8" s="258" t="s">
+      <c r="E8" s="171" t="s">
         <v>316</v>
       </c>
       <c r="F8" s="102"/>
       <c r="G8" s="103"/>
     </row>
     <row r="9" spans="1:8" ht="290.25">
-      <c r="A9" s="256">
+      <c r="A9" s="169">
         <v>7</v>
       </c>
-      <c r="B9" s="253" t="s">
+      <c r="B9" s="166" t="s">
         <v>317</v>
       </c>
-      <c r="C9" s="257" t="s">
+      <c r="C9" s="170" t="s">
         <v>318</v>
       </c>
-      <c r="D9" s="257" t="s">
+      <c r="D9" s="170" t="s">
         <v>300</v>
       </c>
-      <c r="E9" s="258" t="s">
+      <c r="E9" s="171" t="s">
         <v>319</v>
       </c>
       <c r="F9" s="102"/>
       <c r="G9" s="103"/>
     </row>
     <row r="10" spans="1:8" ht="321">
-      <c r="A10" s="256">
+      <c r="A10" s="169">
         <v>8</v>
       </c>
-      <c r="B10" s="253" t="s">
+      <c r="B10" s="166" t="s">
         <v>320</v>
       </c>
-      <c r="C10" s="257" t="s">
+      <c r="C10" s="170" t="s">
         <v>321</v>
       </c>
-      <c r="D10" s="257" t="s">
+      <c r="D10" s="170" t="s">
         <v>300</v>
       </c>
-      <c r="E10" s="258" t="s">
+      <c r="E10" s="171" t="s">
         <v>322</v>
       </c>
       <c r="F10" s="102"/>
       <c r="G10" s="103"/>
     </row>
     <row r="11" spans="1:8" ht="275.25">
-      <c r="A11" s="256">
+      <c r="A11" s="169">
         <v>9</v>
       </c>
-      <c r="B11" s="253" t="s">
+      <c r="B11" s="166" t="s">
         <v>323</v>
       </c>
-      <c r="C11" s="257" t="s">
+      <c r="C11" s="170" t="s">
         <v>324</v>
       </c>
-      <c r="D11" s="257" t="s">
+      <c r="D11" s="170" t="s">
         <v>300</v>
       </c>
-      <c r="E11" s="258" t="s">
+      <c r="E11" s="171" t="s">
         <v>325</v>
       </c>
       <c r="F11" s="104"/>
       <c r="G11" s="105"/>
     </row>
     <row r="12" spans="1:8" ht="148.5">
-      <c r="A12" s="256">
+      <c r="A12" s="169">
         <v>10</v>
       </c>
-      <c r="B12" s="259" t="s">
+      <c r="B12" s="172" t="s">
         <v>326</v>
       </c>
-      <c r="C12" s="257" t="s">
+      <c r="C12" s="170" t="s">
         <v>327</v>
       </c>
-      <c r="D12" s="257" t="s">
+      <c r="D12" s="170" t="s">
         <v>328</v>
       </c>
-      <c r="E12" s="258" t="s">
+      <c r="E12" s="171" t="s">
         <v>329</v>
       </c>
       <c r="F12" s="145"/>
       <c r="G12" s="105"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
-      <c r="A13" s="220" t="s">
+      <c r="A13" s="236" t="s">
         <v>226</v>
       </c>
-      <c r="B13" s="220"/>
-      <c r="C13" s="220"/>
-      <c r="D13" s="220"/>
-      <c r="E13" s="220"/>
-      <c r="F13" s="220"/>
+      <c r="B13" s="236"/>
+      <c r="C13" s="236"/>
+      <c r="D13" s="236"/>
+      <c r="E13" s="236"/>
+      <c r="F13" s="236"/>
       <c r="G13" s="152"/>
     </row>
     <row r="14" spans="1:8" ht="27">
@@ -13272,6 +13263,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
@@ -13281,7 +13281,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -13453,23 +13453,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
 </file>